--- a/NWJSSP_JuanLlorente_GRASP.xlsx
+++ b/NWJSSP_JuanLlorente_GRASP.xlsx
@@ -359,7 +359,7 @@
         <v>314</v>
       </c>
       <c r="B1">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -394,312 +394,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>5560338</v>
+        <v>5466025</v>
       </c>
       <c r="B1">
-        <v>35797</v>
+        <v>18378</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>53634</v>
+        <v>11427</v>
       </c>
       <c r="B2">
-        <v>77862</v>
+        <v>14617</v>
       </c>
       <c r="C2">
-        <v>10453</v>
+        <v>107678</v>
       </c>
       <c r="D2">
-        <v>3743</v>
+        <v>6893</v>
       </c>
       <c r="E2">
-        <v>105522</v>
+        <v>78489</v>
       </c>
       <c r="F2">
-        <v>59662</v>
+        <v>70414</v>
       </c>
       <c r="G2">
-        <v>63329</v>
+        <v>17747</v>
       </c>
       <c r="H2">
-        <v>9781</v>
+        <v>1654</v>
       </c>
       <c r="I2">
-        <v>29966</v>
+        <v>55899</v>
       </c>
       <c r="J2">
-        <v>89080</v>
+        <v>88287</v>
       </c>
       <c r="K2">
-        <v>39002</v>
+        <v>22924</v>
       </c>
       <c r="L2">
-        <v>82662</v>
+        <v>5290</v>
       </c>
       <c r="M2">
-        <v>19423</v>
+        <v>79622</v>
       </c>
       <c r="N2">
-        <v>28300</v>
+        <v>41435</v>
       </c>
       <c r="O2">
-        <v>105025</v>
+        <v>100449</v>
       </c>
       <c r="P2">
-        <v>14340</v>
+        <v>51836</v>
       </c>
       <c r="Q2">
-        <v>80509</v>
+        <v>67438</v>
       </c>
       <c r="R2">
-        <v>79965</v>
+        <v>67219</v>
       </c>
       <c r="S2">
-        <v>75709</v>
+        <v>37183</v>
       </c>
       <c r="T2">
-        <v>58375</v>
+        <v>91256</v>
       </c>
       <c r="U2">
-        <v>76605</v>
+        <v>35890</v>
       </c>
       <c r="V2">
-        <v>9082</v>
+        <v>40012</v>
       </c>
       <c r="W2">
-        <v>32901</v>
+        <v>17338</v>
       </c>
       <c r="X2">
-        <v>45516</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>99614</v>
+        <v>102875</v>
       </c>
       <c r="Z2">
-        <v>54434</v>
+        <v>95438</v>
       </c>
       <c r="AA2">
-        <v>48102</v>
+        <v>83423</v>
       </c>
       <c r="AB2">
-        <v>13709</v>
+        <v>74443</v>
       </c>
       <c r="AC2">
+        <v>39219</v>
+      </c>
+      <c r="AD2">
+        <v>90060</v>
+      </c>
+      <c r="AE2">
+        <v>35910</v>
+      </c>
+      <c r="AF2">
+        <v>12322</v>
+      </c>
+      <c r="AG2">
+        <v>87593</v>
+      </c>
+      <c r="AH2">
+        <v>14945</v>
+      </c>
+      <c r="AI2">
+        <v>27832</v>
+      </c>
+      <c r="AJ2">
+        <v>49734</v>
+      </c>
+      <c r="AK2">
+        <v>58836</v>
+      </c>
+      <c r="AL2">
+        <v>81684</v>
+      </c>
+      <c r="AM2">
+        <v>56846</v>
+      </c>
+      <c r="AN2">
+        <v>13136</v>
+      </c>
+      <c r="AO2">
+        <v>77581</v>
+      </c>
+      <c r="AP2">
+        <v>107686</v>
+      </c>
+      <c r="AQ2">
+        <v>95165</v>
+      </c>
+      <c r="AR2">
+        <v>20585</v>
+      </c>
+      <c r="AS2">
+        <v>63905</v>
+      </c>
+      <c r="AT2">
+        <v>70683</v>
+      </c>
+      <c r="AU2">
+        <v>46951</v>
+      </c>
+      <c r="AV2">
+        <v>10142</v>
+      </c>
+      <c r="AW2">
+        <v>5836</v>
+      </c>
+      <c r="AX2">
+        <v>73279</v>
+      </c>
+      <c r="AY2">
+        <v>68535</v>
+      </c>
+      <c r="AZ2">
+        <v>45479</v>
+      </c>
+      <c r="BA2">
+        <v>56528</v>
+      </c>
+      <c r="BB2">
+        <v>34814</v>
+      </c>
+      <c r="BC2">
+        <v>28270</v>
+      </c>
+      <c r="BD2">
+        <v>49565</v>
+      </c>
+      <c r="BE2">
+        <v>53938</v>
+      </c>
+      <c r="BF2">
+        <v>91798</v>
+      </c>
+      <c r="BG2">
+        <v>18</v>
+      </c>
+      <c r="BH2">
+        <v>52812</v>
+      </c>
+      <c r="BI2">
+        <v>23795</v>
+      </c>
+      <c r="BJ2">
+        <v>563</v>
+      </c>
+      <c r="BK2">
+        <v>47370</v>
+      </c>
+      <c r="BL2">
+        <v>93484</v>
+      </c>
+      <c r="BM2">
+        <v>53325</v>
+      </c>
+      <c r="BN2">
+        <v>62884</v>
+      </c>
+      <c r="BO2">
+        <v>84737</v>
+      </c>
+      <c r="BP2">
+        <v>33177</v>
+      </c>
+      <c r="BQ2">
+        <v>8490</v>
+      </c>
+      <c r="BR2">
+        <v>15710</v>
+      </c>
+      <c r="BS2">
+        <v>86053</v>
+      </c>
+      <c r="BT2">
+        <v>63513</v>
+      </c>
+      <c r="BU2">
+        <v>19741</v>
+      </c>
+      <c r="BV2">
+        <v>99528</v>
+      </c>
+      <c r="BW2">
+        <v>43317</v>
+      </c>
+      <c r="BX2">
+        <v>98329</v>
+      </c>
+      <c r="BY2">
         <v>0</v>
       </c>
-      <c r="AD2">
-        <v>65251</v>
-      </c>
-      <c r="AE2">
-        <v>71005</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>86259</v>
-      </c>
-      <c r="AH2">
-        <v>91784</v>
-      </c>
-      <c r="AI2">
-        <v>17321</v>
-      </c>
-      <c r="AJ2">
-        <v>84354</v>
-      </c>
-      <c r="AK2">
-        <v>19096</v>
-      </c>
-      <c r="AL2">
-        <v>87192</v>
-      </c>
-      <c r="AM2">
-        <v>33597</v>
-      </c>
-      <c r="AN2">
-        <v>35372</v>
-      </c>
-      <c r="AO2">
-        <v>27404</v>
-      </c>
-      <c r="AP2">
-        <v>94950</v>
-      </c>
-      <c r="AQ2">
-        <v>88622</v>
-      </c>
-      <c r="AR2">
-        <v>57965</v>
-      </c>
-      <c r="AS2">
-        <v>12005</v>
-      </c>
-      <c r="AT2">
-        <v>43122</v>
-      </c>
-      <c r="AU2">
-        <v>46745</v>
-      </c>
-      <c r="AV2">
-        <v>26537</v>
-      </c>
-      <c r="AW2">
-        <v>477</v>
-      </c>
-      <c r="AX2">
-        <v>30490</v>
-      </c>
-      <c r="AY2">
-        <v>92537</v>
-      </c>
-      <c r="AZ2">
-        <v>97848</v>
-      </c>
-      <c r="BA2">
-        <v>70441</v>
-      </c>
-      <c r="BB2">
-        <v>21011</v>
-      </c>
-      <c r="BC2">
-        <v>6463</v>
-      </c>
-      <c r="BD2">
-        <v>41623</v>
-      </c>
-      <c r="BE2">
-        <v>54925</v>
-      </c>
-      <c r="BF2">
-        <v>2359</v>
-      </c>
-      <c r="BG2">
-        <v>67176</v>
-      </c>
-      <c r="BH2">
-        <v>81937</v>
-      </c>
-      <c r="BI2">
-        <v>111023</v>
-      </c>
-      <c r="BJ2">
-        <v>109365</v>
-      </c>
-      <c r="BK2">
-        <v>61690</v>
-      </c>
-      <c r="BL2">
-        <v>101320</v>
-      </c>
-      <c r="BM2">
-        <v>40452</v>
-      </c>
-      <c r="BN2">
-        <v>24336</v>
-      </c>
-      <c r="BO2">
-        <v>91105</v>
-      </c>
-      <c r="BP2">
-        <v>30918</v>
-      </c>
-      <c r="BQ2">
-        <v>24885</v>
-      </c>
-      <c r="BR2">
-        <v>23228</v>
-      </c>
-      <c r="BS2">
-        <v>56914</v>
-      </c>
-      <c r="BT2">
-        <v>45230</v>
-      </c>
-      <c r="BU2">
-        <v>34880</v>
-      </c>
-      <c r="BV2">
-        <v>73557</v>
-      </c>
-      <c r="BW2">
-        <v>17261</v>
-      </c>
-      <c r="BX2">
-        <v>64656</v>
-      </c>
-      <c r="BY2">
-        <v>68354</v>
-      </c>
       <c r="BZ2">
-        <v>50069</v>
+        <v>59764</v>
       </c>
       <c r="CA2">
-        <v>7031</v>
+        <v>87462</v>
       </c>
       <c r="CB2">
-        <v>94223</v>
+        <v>97965</v>
       </c>
       <c r="CC2">
-        <v>42299</v>
+        <v>29056</v>
       </c>
       <c r="CD2">
-        <v>2173</v>
+        <v>31273</v>
       </c>
       <c r="CE2">
-        <v>21960</v>
+        <v>44098</v>
       </c>
       <c r="CF2">
-        <v>68843</v>
+        <v>33822</v>
       </c>
       <c r="CG2">
-        <v>48455</v>
+        <v>3289</v>
       </c>
       <c r="CH2">
-        <v>67215</v>
+        <v>19857</v>
       </c>
       <c r="CI2">
-        <v>52399</v>
+        <v>9601</v>
       </c>
       <c r="CJ2">
-        <v>61085</v>
+        <v>25653</v>
       </c>
       <c r="CK2">
-        <v>36914</v>
+        <v>21926</v>
       </c>
       <c r="CL2">
-        <v>5462</v>
+        <v>65934</v>
       </c>
       <c r="CM2">
-        <v>102480</v>
+        <v>6415</v>
       </c>
       <c r="CN2">
-        <v>67</v>
+        <v>39156</v>
       </c>
       <c r="CO2">
-        <v>98400</v>
+        <v>26504</v>
       </c>
       <c r="CP2">
-        <v>51460</v>
+        <v>46283</v>
       </c>
       <c r="CQ2">
-        <v>16142</v>
+        <v>76611</v>
       </c>
       <c r="CR2">
-        <v>14935</v>
+        <v>70205</v>
       </c>
       <c r="CS2">
-        <v>55445</v>
+        <v>73651</v>
       </c>
       <c r="CT2">
-        <v>20543</v>
+        <v>4388</v>
       </c>
       <c r="CU2">
-        <v>63136</v>
+        <v>61265</v>
       </c>
       <c r="CV2">
-        <v>73429</v>
+        <v>104142</v>
       </c>
     </row>
   </sheetData>
@@ -714,312 +714,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>34243071</v>
+        <v>33742555</v>
       </c>
       <c r="B1">
-        <v>1174013</v>
+        <v>562428</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>289776</v>
+        <v>79843</v>
       </c>
       <c r="B2">
-        <v>588503</v>
+        <v>64599</v>
       </c>
       <c r="C2">
-        <v>340730</v>
+        <v>198535</v>
       </c>
       <c r="D2">
-        <v>487686</v>
+        <v>515255</v>
       </c>
       <c r="E2">
-        <v>576345</v>
+        <v>478498</v>
       </c>
       <c r="F2">
-        <v>322428</v>
+        <v>95678</v>
       </c>
       <c r="G2">
-        <v>102595</v>
+        <v>532603</v>
       </c>
       <c r="H2">
-        <v>220085</v>
+        <v>408959</v>
       </c>
       <c r="I2">
-        <v>73582</v>
+        <v>132498</v>
       </c>
       <c r="J2">
-        <v>271946</v>
+        <v>381639</v>
       </c>
       <c r="K2">
-        <v>190626</v>
+        <v>379473</v>
       </c>
       <c r="L2">
-        <v>314354</v>
+        <v>401805</v>
       </c>
       <c r="M2">
-        <v>357872</v>
+        <v>173667</v>
       </c>
       <c r="N2">
-        <v>100037</v>
+        <v>242535</v>
       </c>
       <c r="O2">
-        <v>409013</v>
+        <v>230542</v>
       </c>
       <c r="P2">
-        <v>57466</v>
+        <v>290424</v>
       </c>
       <c r="Q2">
-        <v>35413</v>
+        <v>271363</v>
       </c>
       <c r="R2">
-        <v>529678</v>
+        <v>600211</v>
       </c>
       <c r="S2">
-        <v>256759</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>210115</v>
+        <v>574675</v>
       </c>
       <c r="U2">
-        <v>113016</v>
+        <v>193227</v>
       </c>
       <c r="V2">
-        <v>9009</v>
+        <v>602500</v>
       </c>
       <c r="W2">
-        <v>21879</v>
+        <v>399691</v>
       </c>
       <c r="X2">
-        <v>454248</v>
+        <v>428881</v>
       </c>
       <c r="Y2">
-        <v>175755</v>
+        <v>572360</v>
       </c>
       <c r="Z2">
-        <v>191987</v>
+        <v>41557</v>
       </c>
       <c r="AA2">
-        <v>331888</v>
+        <v>551343</v>
       </c>
       <c r="AB2">
-        <v>123720</v>
+        <v>237822</v>
       </c>
       <c r="AC2">
-        <v>148720</v>
+        <v>144245</v>
       </c>
       <c r="AD2">
-        <v>281778</v>
+        <v>624525</v>
       </c>
       <c r="AE2">
-        <v>620146</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>459997</v>
+        <v>1978</v>
       </c>
       <c r="AG2">
-        <v>187149</v>
+        <v>105083</v>
       </c>
       <c r="AH2">
-        <v>136117</v>
+        <v>276718</v>
       </c>
       <c r="AI2">
-        <v>232957</v>
+        <v>522569</v>
       </c>
       <c r="AJ2">
-        <v>242282</v>
+        <v>328189</v>
       </c>
       <c r="AK2">
-        <v>274696</v>
+        <v>558190</v>
       </c>
       <c r="AL2">
-        <v>573596</v>
+        <v>141440</v>
       </c>
       <c r="AM2">
-        <v>428001</v>
+        <v>4704</v>
       </c>
       <c r="AN2">
-        <v>143085</v>
+        <v>58136</v>
       </c>
       <c r="AO2">
-        <v>636413</v>
+        <v>358746</v>
       </c>
       <c r="AP2">
-        <v>299012</v>
+        <v>511521</v>
       </c>
       <c r="AQ2">
-        <v>346372</v>
+        <v>898</v>
       </c>
       <c r="AR2">
-        <v>38845</v>
+        <v>52882</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>120272</v>
       </c>
       <c r="AT2">
-        <v>38224</v>
+        <v>294203</v>
       </c>
       <c r="AU2">
-        <v>1903</v>
+        <v>330396</v>
       </c>
       <c r="AV2">
-        <v>143506</v>
+        <v>28929</v>
       </c>
       <c r="AW2">
-        <v>412136</v>
+        <v>310198</v>
       </c>
       <c r="AX2">
-        <v>395577</v>
+        <v>586729</v>
       </c>
       <c r="AY2">
-        <v>509609</v>
+        <v>426361</v>
       </c>
       <c r="AZ2">
-        <v>503102</v>
+        <v>284331</v>
       </c>
       <c r="BA2">
-        <v>533380</v>
+        <v>455015</v>
       </c>
       <c r="BB2">
-        <v>71928</v>
+        <v>11348</v>
       </c>
       <c r="BC2">
-        <v>495239</v>
+        <v>163524</v>
       </c>
       <c r="BD2">
-        <v>171610</v>
+        <v>19741</v>
       </c>
       <c r="BE2">
-        <v>89338</v>
+        <v>209712</v>
       </c>
       <c r="BF2">
-        <v>368708</v>
+        <v>71225</v>
       </c>
       <c r="BG2">
-        <v>428438</v>
+        <v>563023</v>
       </c>
       <c r="BH2">
-        <v>6162</v>
+        <v>211204</v>
       </c>
       <c r="BI2">
-        <v>547906</v>
+        <v>347523</v>
       </c>
       <c r="BJ2">
-        <v>14672</v>
+        <v>417501</v>
       </c>
       <c r="BK2">
-        <v>583303</v>
+        <v>263891</v>
       </c>
       <c r="BL2">
-        <v>164931</v>
+        <v>322922</v>
       </c>
       <c r="BM2">
-        <v>458912</v>
+        <v>43052</v>
       </c>
       <c r="BN2">
-        <v>373899</v>
+        <v>88215</v>
       </c>
       <c r="BO2">
-        <v>471732</v>
+        <v>497963</v>
       </c>
       <c r="BP2">
-        <v>302127</v>
+        <v>295377</v>
       </c>
       <c r="BQ2">
-        <v>72370</v>
+        <v>188275</v>
       </c>
       <c r="BR2">
-        <v>526022</v>
+        <v>1141</v>
       </c>
       <c r="BS2">
-        <v>556030</v>
+        <v>444529</v>
       </c>
       <c r="BT2">
-        <v>0</v>
+        <v>339447</v>
       </c>
       <c r="BU2">
-        <v>330315</v>
+        <v>371144</v>
       </c>
       <c r="BV2">
-        <v>301139</v>
+        <v>107583</v>
       </c>
       <c r="BW2">
-        <v>418943</v>
+        <v>225193</v>
       </c>
       <c r="BX2">
-        <v>359041</v>
+        <v>305670</v>
       </c>
       <c r="BY2">
-        <v>560466</v>
+        <v>446746</v>
       </c>
       <c r="BZ2">
-        <v>167889</v>
+        <v>134893</v>
       </c>
       <c r="CA2">
-        <v>608317</v>
+        <v>466721</v>
       </c>
       <c r="CB2">
-        <v>209555</v>
+        <v>198641</v>
       </c>
       <c r="CC2">
-        <v>204788</v>
+        <v>484380</v>
       </c>
       <c r="CD2">
-        <v>119352</v>
+        <v>254018</v>
       </c>
       <c r="CE2">
-        <v>53302</v>
+        <v>37984</v>
       </c>
       <c r="CF2">
-        <v>240533</v>
+        <v>152775</v>
       </c>
       <c r="CG2">
-        <v>94415</v>
+        <v>470988</v>
       </c>
       <c r="CH2">
-        <v>58986</v>
+        <v>240049</v>
       </c>
       <c r="CI2">
-        <v>130763</v>
+        <v>539410</v>
       </c>
       <c r="CJ2">
-        <v>265852</v>
+        <v>434238</v>
       </c>
       <c r="CK2">
-        <v>440359</v>
+        <v>83985</v>
       </c>
       <c r="CL2">
-        <v>507874</v>
+        <v>364497</v>
       </c>
       <c r="CM2">
-        <v>226001</v>
+        <v>393135</v>
       </c>
       <c r="CN2">
-        <v>505</v>
+        <v>165718</v>
       </c>
       <c r="CO2">
-        <v>328841</v>
+        <v>209345</v>
       </c>
       <c r="CP2">
-        <v>392239</v>
+        <v>170651</v>
       </c>
       <c r="CQ2">
-        <v>628067</v>
+        <v>540624</v>
       </c>
       <c r="CR2">
-        <v>481306</v>
+        <v>119162</v>
       </c>
       <c r="CS2">
-        <v>251439</v>
+        <v>614695</v>
       </c>
       <c r="CT2">
-        <v>431347</v>
+        <v>355124</v>
       </c>
       <c r="CU2">
-        <v>381145</v>
+        <v>254089</v>
       </c>
       <c r="CV2">
-        <v>605183</v>
+        <v>496375</v>
       </c>
     </row>
   </sheetData>
@@ -1034,312 +1034,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>33979418</v>
+        <v>34195381</v>
       </c>
       <c r="B1">
-        <v>1159221</v>
+        <v>532974</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>478810</v>
+        <v>264340</v>
       </c>
       <c r="B2">
-        <v>49398</v>
+        <v>4731</v>
       </c>
       <c r="C2">
-        <v>128902</v>
+        <v>630626</v>
       </c>
       <c r="D2">
-        <v>114848</v>
+        <v>372224</v>
       </c>
       <c r="E2">
-        <v>560744</v>
+        <v>429719</v>
       </c>
       <c r="F2">
-        <v>377783</v>
+        <v>201934</v>
       </c>
       <c r="G2">
-        <v>325742</v>
+        <v>1270</v>
       </c>
       <c r="H2">
-        <v>10379</v>
+        <v>158346</v>
       </c>
       <c r="I2">
-        <v>534227</v>
+        <v>220483</v>
       </c>
       <c r="J2">
-        <v>164385</v>
+        <v>367939</v>
       </c>
       <c r="K2">
-        <v>233412</v>
+        <v>249248</v>
       </c>
       <c r="L2">
-        <v>624098</v>
+        <v>391380</v>
       </c>
       <c r="M2">
-        <v>500287</v>
+        <v>245707</v>
       </c>
       <c r="N2">
-        <v>525170</v>
+        <v>285957</v>
       </c>
       <c r="O2">
-        <v>424516</v>
+        <v>346644</v>
       </c>
       <c r="P2">
-        <v>187310</v>
+        <v>505179</v>
       </c>
       <c r="Q2">
-        <v>124217</v>
+        <v>599353</v>
       </c>
       <c r="R2">
-        <v>622577</v>
+        <v>76933</v>
       </c>
       <c r="S2">
-        <v>439468</v>
+        <v>234945</v>
       </c>
       <c r="T2">
-        <v>508277</v>
+        <v>551707</v>
       </c>
       <c r="U2">
-        <v>199327</v>
+        <v>138176</v>
       </c>
       <c r="V2">
-        <v>237669</v>
+        <v>364463</v>
       </c>
       <c r="W2">
-        <v>358031</v>
+        <v>403422</v>
       </c>
       <c r="X2">
-        <v>433307</v>
+        <v>580080</v>
       </c>
       <c r="Y2">
-        <v>524037</v>
+        <v>403142</v>
       </c>
       <c r="Z2">
-        <v>560625</v>
+        <v>491422</v>
       </c>
       <c r="AA2">
-        <v>36142</v>
+        <v>612942</v>
       </c>
       <c r="AB2">
-        <v>78073</v>
+        <v>71245</v>
       </c>
       <c r="AC2">
-        <v>72100</v>
+        <v>415612</v>
       </c>
       <c r="AD2">
-        <v>339724</v>
+        <v>157956</v>
       </c>
       <c r="AE2">
-        <v>227386</v>
+        <v>23176</v>
       </c>
       <c r="AF2">
-        <v>580141</v>
+        <v>469516</v>
       </c>
       <c r="AG2">
-        <v>607521</v>
+        <v>241192</v>
       </c>
       <c r="AH2">
-        <v>160531</v>
+        <v>469735</v>
       </c>
       <c r="AI2">
+        <v>420324</v>
+      </c>
+      <c r="AJ2">
+        <v>342887</v>
+      </c>
+      <c r="AK2">
+        <v>50058</v>
+      </c>
+      <c r="AL2">
+        <v>588945</v>
+      </c>
+      <c r="AM2">
+        <v>497226</v>
+      </c>
+      <c r="AN2">
+        <v>89701</v>
+      </c>
+      <c r="AO2">
+        <v>455433</v>
+      </c>
+      <c r="AP2">
+        <v>519421</v>
+      </c>
+      <c r="AQ2">
+        <v>93823</v>
+      </c>
+      <c r="AR2">
+        <v>120925</v>
+      </c>
+      <c r="AS2">
+        <v>283671</v>
+      </c>
+      <c r="AT2">
+        <v>131994</v>
+      </c>
+      <c r="AU2">
         <v>0</v>
       </c>
-      <c r="AJ2">
-        <v>387228</v>
-      </c>
-      <c r="AK2">
-        <v>349189</v>
-      </c>
-      <c r="AL2">
-        <v>290927</v>
-      </c>
-      <c r="AM2">
-        <v>348390</v>
-      </c>
-      <c r="AN2">
-        <v>103866</v>
-      </c>
-      <c r="AO2">
-        <v>315763</v>
-      </c>
-      <c r="AP2">
-        <v>305357</v>
-      </c>
-      <c r="AQ2">
-        <v>91833</v>
-      </c>
-      <c r="AR2">
-        <v>171689</v>
-      </c>
-      <c r="AS2">
-        <v>364466</v>
-      </c>
-      <c r="AT2">
-        <v>420740</v>
-      </c>
-      <c r="AU2">
-        <v>489820</v>
-      </c>
       <c r="AV2">
-        <v>57901</v>
+        <v>339931</v>
       </c>
       <c r="AW2">
-        <v>98918</v>
+        <v>487936</v>
       </c>
       <c r="AX2">
-        <v>55334</v>
+        <v>212285</v>
       </c>
       <c r="AY2">
-        <v>267222</v>
+        <v>2579</v>
       </c>
       <c r="AZ2">
-        <v>265861</v>
+        <v>298784</v>
       </c>
       <c r="BA2">
-        <v>428546</v>
+        <v>79082</v>
       </c>
       <c r="BB2">
-        <v>311903</v>
+        <v>108195</v>
       </c>
       <c r="BC2">
-        <v>209990</v>
+        <v>327223</v>
       </c>
       <c r="BD2">
-        <v>467998</v>
+        <v>207012</v>
       </c>
       <c r="BE2">
-        <v>56435</v>
+        <v>125912</v>
       </c>
       <c r="BF2">
-        <v>85755</v>
+        <v>109276</v>
       </c>
       <c r="BG2">
-        <v>18355</v>
+        <v>101208</v>
       </c>
       <c r="BH2">
-        <v>334213</v>
+        <v>201085</v>
       </c>
       <c r="BI2">
-        <v>186724</v>
+        <v>2891</v>
       </c>
       <c r="BJ2">
-        <v>301936</v>
+        <v>444836</v>
       </c>
       <c r="BK2">
-        <v>366581</v>
+        <v>143948</v>
       </c>
       <c r="BL2">
-        <v>238220</v>
+        <v>248173</v>
       </c>
       <c r="BM2">
-        <v>140858</v>
+        <v>552560</v>
       </c>
       <c r="BN2">
-        <v>84720</v>
+        <v>438495</v>
       </c>
       <c r="BO2">
-        <v>253223</v>
+        <v>643969</v>
       </c>
       <c r="BP2">
-        <v>603569</v>
+        <v>270594</v>
       </c>
       <c r="BQ2">
-        <v>454187</v>
+        <v>58952</v>
       </c>
       <c r="BR2">
-        <v>140047</v>
+        <v>311625</v>
       </c>
       <c r="BS2">
-        <v>42747</v>
+        <v>383324</v>
       </c>
       <c r="BT2">
-        <v>417080</v>
+        <v>525985</v>
       </c>
       <c r="BU2">
-        <v>247472</v>
+        <v>523200</v>
       </c>
       <c r="BV2">
-        <v>455713</v>
+        <v>471783</v>
       </c>
       <c r="BW2">
-        <v>8861</v>
+        <v>140976</v>
       </c>
       <c r="BX2">
-        <v>469721</v>
+        <v>39767</v>
       </c>
       <c r="BY2">
-        <v>569130</v>
+        <v>592251</v>
       </c>
       <c r="BZ2">
-        <v>404216</v>
+        <v>28426</v>
       </c>
       <c r="CA2">
-        <v>0</v>
+        <v>574410</v>
       </c>
       <c r="CB2">
-        <v>107309</v>
+        <v>189922</v>
       </c>
       <c r="CC2">
-        <v>153491</v>
+        <v>328360</v>
       </c>
       <c r="CD2">
-        <v>273214</v>
+        <v>361871</v>
       </c>
       <c r="CE2">
-        <v>0</v>
+        <v>181807</v>
       </c>
       <c r="CF2">
-        <v>218107</v>
+        <v>1074</v>
       </c>
       <c r="CG2">
-        <v>48163</v>
+        <v>451352</v>
       </c>
       <c r="CH2">
-        <v>203038</v>
+        <v>501106</v>
       </c>
       <c r="CI2">
-        <v>297096</v>
+        <v>189243</v>
       </c>
       <c r="CJ2">
-        <v>587900</v>
+        <v>163726</v>
       </c>
       <c r="CK2">
-        <v>547423</v>
+        <v>168663</v>
       </c>
       <c r="CL2">
-        <v>390503</v>
+        <v>34187</v>
       </c>
       <c r="CM2">
-        <v>179251</v>
+        <v>61587</v>
       </c>
       <c r="CN2">
-        <v>507363</v>
+        <v>38183</v>
       </c>
       <c r="CO2">
-        <v>33826</v>
+        <v>277073</v>
       </c>
       <c r="CP2">
-        <v>398574</v>
+        <v>300974</v>
       </c>
       <c r="CQ2">
-        <v>576908</v>
+        <v>319237</v>
       </c>
       <c r="CR2">
-        <v>521082</v>
+        <v>541082</v>
       </c>
       <c r="CS2">
-        <v>143225</v>
+        <v>422967</v>
       </c>
       <c r="CT2">
-        <v>5616</v>
+        <v>236440</v>
       </c>
       <c r="CU2">
-        <v>473656</v>
+        <v>561820</v>
       </c>
       <c r="CV2">
-        <v>283137</v>
+        <v>294214</v>
       </c>
     </row>
   </sheetData>
@@ -1357,7 +1357,7 @@
         <v>346</v>
       </c>
       <c r="B1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -1392,42 +1392,42 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>10233</v>
+        <v>10565</v>
       </c>
       <c r="B1">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
+        <v>436</v>
+      </c>
+      <c r="B2">
+        <v>142</v>
+      </c>
+      <c r="C2">
+        <v>543</v>
+      </c>
+      <c r="D2">
+        <v>1266</v>
+      </c>
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="B2">
-        <v>155</v>
-      </c>
-      <c r="C2">
-        <v>1089</v>
-      </c>
-      <c r="D2">
-        <v>933</v>
-      </c>
-      <c r="E2">
-        <v>839</v>
-      </c>
       <c r="F2">
-        <v>709</v>
+        <v>907</v>
       </c>
       <c r="G2">
-        <v>506</v>
+        <v>750</v>
       </c>
       <c r="H2">
-        <v>558</v>
+        <v>1103</v>
       </c>
       <c r="I2">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J2">
-        <v>297</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -1442,42 +1442,42 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>11091</v>
+        <v>10897</v>
       </c>
       <c r="B1">
-        <v>45</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2">
-        <v>849</v>
+        <v>0</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="C2">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="D2">
-        <v>956</v>
+        <v>1079</v>
       </c>
       <c r="E2">
-        <v>1569</v>
+        <v>991</v>
       </c>
       <c r="F2">
-        <v>166</v>
+        <v>855</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>506</v>
       </c>
       <c r="H2">
-        <v>402</v>
+        <v>1315</v>
       </c>
       <c r="I2">
-        <v>263</v>
+        <v>38</v>
       </c>
       <c r="J2">
-        <v>1197</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -1492,72 +1492,72 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1">
-        <v>19865</v>
+        <v>20188</v>
       </c>
       <c r="B1">
-        <v>122</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>1540</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>485</v>
+        <v>362</v>
       </c>
       <c r="C2">
-        <v>703</v>
+        <v>119</v>
       </c>
       <c r="D2">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>519</v>
+        <v>875</v>
       </c>
       <c r="G2">
-        <v>1069</v>
+        <v>605</v>
       </c>
       <c r="H2">
-        <v>371</v>
+        <v>1706</v>
       </c>
       <c r="I2">
-        <v>596</v>
+        <v>473</v>
       </c>
       <c r="J2">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="K2">
-        <v>450</v>
+        <v>318</v>
       </c>
       <c r="L2">
-        <v>1439</v>
+        <v>785</v>
       </c>
       <c r="M2">
-        <v>208</v>
+        <v>943</v>
       </c>
       <c r="N2">
-        <v>14</v>
+        <v>1274</v>
       </c>
       <c r="O2">
-        <v>1203</v>
+        <v>1028</v>
       </c>
       <c r="P2">
-        <v>917</v>
+        <v>1521</v>
       </c>
       <c r="Q2">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="R2">
-        <v>833</v>
+        <v>712</v>
       </c>
       <c r="S2">
-        <v>1319</v>
+        <v>45</v>
       </c>
       <c r="T2">
-        <v>89</v>
+        <v>1349</v>
       </c>
     </row>
   </sheetData>
@@ -1572,72 +1572,72 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1">
-        <v>19595</v>
+        <v>20057</v>
       </c>
       <c r="B1">
-        <v>111</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2">
-        <v>1628</v>
+        <v>621</v>
       </c>
       <c r="B2">
-        <v>1433</v>
+        <v>119</v>
       </c>
       <c r="C2">
-        <v>65</v>
+        <v>868</v>
       </c>
       <c r="D2">
-        <v>346</v>
+        <v>382</v>
       </c>
       <c r="E2">
-        <v>1067</v>
+        <v>1210</v>
       </c>
       <c r="F2">
-        <v>945</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>485</v>
+        <v>667</v>
       </c>
       <c r="H2">
-        <v>1715</v>
+        <v>493</v>
       </c>
       <c r="I2">
-        <v>956</v>
+        <v>1390</v>
       </c>
       <c r="J2">
-        <v>539</v>
+        <v>721</v>
       </c>
       <c r="K2">
-        <v>180</v>
+        <v>572</v>
       </c>
       <c r="L2">
-        <v>855</v>
+        <v>1088</v>
       </c>
       <c r="M2">
-        <v>305</v>
+        <v>330</v>
       </c>
       <c r="N2">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="O2">
-        <v>619</v>
+        <v>801</v>
       </c>
       <c r="P2">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="Q2">
-        <v>1286</v>
+        <v>1684</v>
       </c>
       <c r="R2">
-        <v>1176</v>
+        <v>998</v>
       </c>
       <c r="S2">
-        <v>735</v>
+        <v>1246</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -1652,10 +1652,10 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1">
-        <v>100564</v>
+        <v>105801</v>
       </c>
       <c r="B1">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1663,31 +1663,31 @@
         <v>0</v>
       </c>
       <c r="B2">
+        <v>84</v>
+      </c>
+      <c r="C2">
+        <v>4650</v>
+      </c>
+      <c r="D2">
+        <v>5992</v>
+      </c>
+      <c r="E2">
+        <v>13509</v>
+      </c>
+      <c r="F2">
+        <v>6897</v>
+      </c>
+      <c r="G2">
+        <v>10131</v>
+      </c>
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="C2">
-        <v>5995</v>
-      </c>
-      <c r="D2">
-        <v>7627</v>
-      </c>
-      <c r="E2">
-        <v>6141</v>
-      </c>
-      <c r="F2">
-        <v>8658</v>
-      </c>
-      <c r="G2">
-        <v>3817</v>
-      </c>
-      <c r="H2">
-        <v>3820</v>
-      </c>
       <c r="I2">
-        <v>1037</v>
+        <v>2714</v>
       </c>
       <c r="J2">
-        <v>10714</v>
+        <v>9069</v>
       </c>
     </row>
   </sheetData>
@@ -1705,7 +1705,7 @@
         <v>104562</v>
       </c>
       <c r="B1">
-        <v>31</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -1752,312 +1752,312 @@
   <sheetData>
     <row r="1" spans="1:100">
       <c r="A1">
-        <v>5472683</v>
+        <v>5453744</v>
       </c>
       <c r="B1">
-        <v>36328</v>
+        <v>17767</v>
       </c>
     </row>
     <row r="2" spans="1:100">
       <c r="A2">
-        <v>97553</v>
+        <v>88816</v>
       </c>
       <c r="B2">
-        <v>28466</v>
+        <v>45903</v>
       </c>
       <c r="C2">
-        <v>6727</v>
+        <v>39016</v>
       </c>
       <c r="D2">
-        <v>69488</v>
+        <v>103304</v>
       </c>
       <c r="E2">
-        <v>18279</v>
+        <v>26608</v>
       </c>
       <c r="F2">
-        <v>95516</v>
+        <v>9368</v>
       </c>
       <c r="G2">
-        <v>13628</v>
+        <v>78962</v>
       </c>
       <c r="H2">
-        <v>25912</v>
+        <v>16822</v>
       </c>
       <c r="I2">
-        <v>81126</v>
+        <v>72921</v>
       </c>
       <c r="J2">
-        <v>87288</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>85645</v>
+        <v>44411</v>
       </c>
       <c r="L2">
-        <v>48744</v>
+        <v>13280</v>
       </c>
       <c r="M2">
-        <v>79675</v>
+        <v>63885</v>
       </c>
       <c r="N2">
-        <v>73827</v>
+        <v>66989</v>
       </c>
       <c r="O2">
-        <v>7858</v>
+        <v>91438</v>
       </c>
       <c r="P2">
-        <v>3850</v>
+        <v>13594</v>
       </c>
       <c r="Q2">
-        <v>54030</v>
+        <v>83252</v>
       </c>
       <c r="R2">
-        <v>25311</v>
+        <v>18841</v>
       </c>
       <c r="S2">
-        <v>10053</v>
+        <v>51391</v>
       </c>
       <c r="T2">
-        <v>78060</v>
+        <v>36296</v>
       </c>
       <c r="U2">
-        <v>58665</v>
+        <v>16659</v>
       </c>
       <c r="V2">
-        <v>91423</v>
+        <v>7326</v>
       </c>
       <c r="W2">
-        <v>94911</v>
+        <v>88002</v>
       </c>
       <c r="X2">
-        <v>9301</v>
+        <v>23345</v>
       </c>
       <c r="Y2">
-        <v>51005</v>
+        <v>32882</v>
       </c>
       <c r="Z2">
-        <v>17796</v>
+        <v>84770</v>
       </c>
       <c r="AA2">
-        <v>1166</v>
+        <v>86798</v>
       </c>
       <c r="AB2">
-        <v>41265</v>
+        <v>39682</v>
       </c>
       <c r="AC2">
-        <v>12783</v>
+        <v>29261</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>52463</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>2714</v>
+        <v>12158</v>
       </c>
       <c r="AG2">
-        <v>90090</v>
+        <v>106323</v>
       </c>
       <c r="AH2">
-        <v>101105</v>
+        <v>70341</v>
       </c>
       <c r="AI2">
-        <v>105148</v>
+        <v>40124</v>
       </c>
       <c r="AJ2">
-        <v>71554</v>
+        <v>58114</v>
       </c>
       <c r="AK2">
-        <v>72838</v>
+        <v>15458</v>
       </c>
       <c r="AL2">
-        <v>11014</v>
+        <v>53285</v>
       </c>
       <c r="AM2">
-        <v>95469</v>
+        <v>60019</v>
       </c>
       <c r="AN2">
-        <v>23931</v>
+        <v>77213</v>
       </c>
       <c r="AO2">
-        <v>39549</v>
+        <v>108640</v>
       </c>
       <c r="AP2">
-        <v>83168</v>
+        <v>82275</v>
       </c>
       <c r="AQ2">
-        <v>34965</v>
+        <v>26245</v>
       </c>
       <c r="AR2">
-        <v>6749</v>
+        <v>268</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>81220</v>
       </c>
       <c r="AT2">
-        <v>76043</v>
+        <v>62696</v>
       </c>
       <c r="AU2">
-        <v>44443</v>
+        <v>46891</v>
       </c>
       <c r="AV2">
-        <v>51694</v>
+        <v>93242</v>
       </c>
       <c r="AW2">
-        <v>58857</v>
+        <v>32642</v>
       </c>
       <c r="AX2">
-        <v>98963</v>
+        <v>56821</v>
       </c>
       <c r="AY2">
-        <v>64736</v>
+        <v>98842</v>
       </c>
       <c r="AZ2">
-        <v>55817</v>
+        <v>5345</v>
       </c>
       <c r="BA2">
-        <v>39352</v>
+        <v>90623</v>
       </c>
       <c r="BB2">
-        <v>110152</v>
+        <v>74711</v>
       </c>
       <c r="BC2">
-        <v>22226</v>
+        <v>23264</v>
       </c>
       <c r="BD2">
-        <v>100862</v>
+        <v>49505</v>
       </c>
       <c r="BE2">
-        <v>47190</v>
+        <v>42863</v>
       </c>
       <c r="BF2">
-        <v>77830</v>
+        <v>29850</v>
       </c>
       <c r="BG2">
-        <v>27</v>
+        <v>52593</v>
       </c>
       <c r="BH2">
-        <v>60936</v>
+        <v>55579</v>
       </c>
       <c r="BI2">
-        <v>15420</v>
+        <v>42237</v>
       </c>
       <c r="BJ2">
-        <v>107074</v>
+        <v>96480</v>
       </c>
       <c r="BK2">
-        <v>20264</v>
+        <v>3993</v>
       </c>
       <c r="BL2">
-        <v>65258</v>
+        <v>29701</v>
       </c>
       <c r="BM2">
-        <v>17001</v>
+        <v>99429</v>
       </c>
       <c r="BN2">
-        <v>26062</v>
+        <v>85820</v>
       </c>
       <c r="BO2">
-        <v>129</v>
+        <v>37490</v>
       </c>
       <c r="BP2">
-        <v>44397</v>
+        <v>74126</v>
       </c>
       <c r="BQ2">
-        <v>54081</v>
+        <v>36407</v>
       </c>
       <c r="BR2">
-        <v>49925</v>
+        <v>100823</v>
       </c>
       <c r="BS2">
-        <v>87939</v>
+        <v>915</v>
       </c>
       <c r="BT2">
-        <v>5837</v>
+        <v>102061</v>
       </c>
       <c r="BU2">
-        <v>82895</v>
+        <v>20957</v>
       </c>
       <c r="BV2">
-        <v>21760</v>
+        <v>11515</v>
       </c>
       <c r="BW2">
-        <v>31720</v>
+        <v>78304</v>
       </c>
       <c r="BX2">
-        <v>89336</v>
+        <v>110651</v>
       </c>
       <c r="BY2">
-        <v>103206</v>
+        <v>61327</v>
       </c>
       <c r="BZ2">
-        <v>3622</v>
+        <v>5944</v>
       </c>
       <c r="CA2">
-        <v>14257</v>
+        <v>95890</v>
       </c>
       <c r="CB2">
-        <v>20291</v>
+        <v>9998</v>
       </c>
       <c r="CC2">
-        <v>60457</v>
+        <v>7277</v>
       </c>
       <c r="CD2">
-        <v>33426</v>
+        <v>69177</v>
       </c>
       <c r="CE2">
-        <v>67672</v>
+        <v>54232</v>
       </c>
       <c r="CF2">
-        <v>86341</v>
+        <v>25066</v>
       </c>
       <c r="CG2">
-        <v>19333</v>
+        <v>20230</v>
       </c>
       <c r="CH2">
-        <v>46797</v>
+        <v>31618</v>
       </c>
       <c r="CI2">
-        <v>30161</v>
+        <v>43467</v>
       </c>
       <c r="CJ2">
-        <v>56320</v>
+        <v>76638</v>
       </c>
       <c r="CK2">
-        <v>42372</v>
+        <v>65667</v>
       </c>
       <c r="CL2">
-        <v>70498</v>
+        <v>3388</v>
       </c>
       <c r="CM2">
-        <v>68176</v>
+        <v>95168</v>
       </c>
       <c r="CN2">
-        <v>37644</v>
+        <v>35385</v>
       </c>
       <c r="CO2">
-        <v>57098</v>
+        <v>38800</v>
       </c>
       <c r="CP2">
-        <v>28980</v>
+        <v>28447</v>
       </c>
       <c r="CQ2">
-        <v>30794</v>
+        <v>22550</v>
       </c>
       <c r="CR2">
-        <v>35164</v>
+        <v>3569</v>
       </c>
       <c r="CS2">
-        <v>74891</v>
+        <v>103494</v>
       </c>
       <c r="CT2">
-        <v>92632</v>
+        <v>71847</v>
       </c>
       <c r="CU2">
-        <v>36360</v>
+        <v>18747</v>
       </c>
       <c r="CV2">
-        <v>63031</v>
+        <v>49111</v>
       </c>
     </row>
   </sheetData>
